--- a/Middleput/games.xlsx
+++ b/Middleput/games.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,6 +1344,66 @@
         <v>9</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45179</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5-a-side</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
